--- a/data/processed/competicoes.xlsx
+++ b/data/processed/competicoes.xlsx
@@ -424,22 +424,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>id_area</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>nome_competicao</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>codigo</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>tipo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>nome_pais</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -452,24 +452,22 @@
       <c r="A2" t="n">
         <v>2013</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>Campeonato Brasileiro Série A</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>BSA</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Brazil</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -482,24 +480,22 @@
       <c r="A3" t="n">
         <v>2016</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="n">
+        <v>2072</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>Championship</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>ELC</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -512,24 +508,22 @@
       <c r="A4" t="n">
         <v>2021</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="n">
+        <v>2072</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>Premier League</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>England</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -542,24 +536,22 @@
       <c r="A5" t="n">
         <v>2001</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="n">
+        <v>2077</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>UEFA Champions League</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>CL</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>CUP</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Europe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,24 +564,22 @@
       <c r="A6" t="n">
         <v>2018</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="n">
+        <v>2077</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>European Championship</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>EC</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>CUP</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Europe</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -602,24 +592,22 @@
       <c r="A7" t="n">
         <v>2015</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="n">
+        <v>2081</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Ligue 1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>FL1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>France</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -632,24 +620,22 @@
       <c r="A8" t="n">
         <v>2002</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="n">
+        <v>2088</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>BL1</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Germany</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -662,24 +648,22 @@
       <c r="A9" t="n">
         <v>2019</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" t="n">
+        <v>2114</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>Serie A</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Italy</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -692,24 +676,22 @@
       <c r="A10" t="n">
         <v>2003</v>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" t="n">
+        <v>2163</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>Eredivisie</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>DED</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -722,24 +704,22 @@
       <c r="A11" t="n">
         <v>2017</v>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2187</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Primeira Liga</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>PPL</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Portugal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -752,24 +732,22 @@
       <c r="A12" t="n">
         <v>2152</v>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>Copa Libertadores</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>CLI</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>CUP</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>South America</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -782,24 +760,22 @@
       <c r="A13" t="n">
         <v>2014</v>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" t="n">
+        <v>2224</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Primera Division</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>PD</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Spain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -812,24 +788,22 @@
       <c r="A14" t="n">
         <v>2000</v>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" t="n">
+        <v>2267</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>FIFA World Cup</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>WC</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>CUP</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>World</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">

--- a/data/processed/competicoes.xlsx
+++ b/data/processed/competicoes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,17 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>codigo</t>
+          <t>codigo_competicao</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
           <t>tipo</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>escudo_url</t>
         </is>
       </c>
     </row>
@@ -468,347 +463,6 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/bsa.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B3" t="n">
-        <v>2072</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Championship</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ELC</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/ELC.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2072</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/PL.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>2001</v>
-      </c>
-      <c r="B5" t="n">
-        <v>2077</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CUP</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/CL.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B6" t="n">
-        <v>2077</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>European Championship</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>EC</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CUP</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/ec.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2081</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FL1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/FL1.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>2002</v>
-      </c>
-      <c r="B8" t="n">
-        <v>2088</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>BL1</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/BL1.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B9" t="n">
-        <v>2114</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Serie A</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>SA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/c111.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>2003</v>
-      </c>
-      <c r="B10" t="n">
-        <v>2163</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Eredivisie</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DED</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/ED.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B11" t="n">
-        <v>2187</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Primeira Liga</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PPL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/PPL.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>2152</v>
-      </c>
-      <c r="B12" t="n">
-        <v>2220</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Copa Libertadores</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CLI</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CUP</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/CLI.svg</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B13" t="n">
-        <v>2224</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Primera Division</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>LEAGUE</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/laliga.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>2000</v>
-      </c>
-      <c r="B14" t="n">
-        <v>2267</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>WC</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CUP</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://crests.football-data.org/wm26.png</t>
         </is>
       </c>
     </row>
